--- a/dataset_t6_grouped/results2/G1/G1_T1912_W0046F0001T0006Z000C1N6_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T1912_W0046F0001T0006Z000C1N6_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>7.002308385334666</v>
+        <v>1.137875112616883</v>
       </c>
       <c r="D2" t="n">
-        <v>30.38422274194904</v>
+        <v>4.937436195566719</v>
       </c>
       <c r="E2" t="n">
-        <v>12.33220961866323</v>
+        <v>2.003984063032775</v>
       </c>
       <c r="F2" t="n">
-        <v>6.832844328264919</v>
+        <v>1.110337203343049</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>29.00347534657253</v>
+        <v>4.713064743818037</v>
       </c>
       <c r="D3" t="n">
-        <v>29.12199187142782</v>
+        <v>4.732323679107021</v>
       </c>
       <c r="E3" t="n">
-        <v>12.33220961866323</v>
+        <v>2.003984063032775</v>
       </c>
       <c r="F3" t="n">
-        <v>6.832844328264919</v>
+        <v>1.110337203343049</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>3.605551275463989</v>
+        <v>0.5859020822628983</v>
       </c>
       <c r="D4" t="n">
-        <v>17.84722020752257</v>
+        <v>2.900173283722418</v>
       </c>
       <c r="E4" t="n">
-        <v>12.33220961866323</v>
+        <v>2.003984063032775</v>
       </c>
       <c r="F4" t="n">
-        <v>6.832844328264919</v>
+        <v>1.110337203343049</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>39.56300340664443</v>
+        <v>6.428988053579721</v>
       </c>
       <c r="D5" t="n">
-        <v>39.50129477982237</v>
+        <v>6.418960401721136</v>
       </c>
       <c r="E5" t="n">
-        <v>12.33220961866323</v>
+        <v>2.003984063032775</v>
       </c>
       <c r="F5" t="n">
-        <v>6.832844328264919</v>
+        <v>1.110337203343049</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>28.46018472994679</v>
+        <v>4.624780018616353</v>
       </c>
       <c r="D6" t="n">
-        <v>29.80296012138281</v>
+        <v>4.842981019724707</v>
       </c>
       <c r="E6" t="n">
-        <v>12.33220961866323</v>
+        <v>2.003984063032775</v>
       </c>
       <c r="F6" t="n">
-        <v>6.832844328264919</v>
+        <v>1.110337203343049</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>36.25563921733972</v>
+        <v>5.891541372817705</v>
       </c>
       <c r="D7" t="n">
-        <v>36.15202779597251</v>
+        <v>5.874704516845533</v>
       </c>
       <c r="E7" t="n">
-        <v>12.33220961866323</v>
+        <v>2.003984063032775</v>
       </c>
       <c r="F7" t="n">
-        <v>6.832844328264919</v>
+        <v>1.110337203343049</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>31.68507097158358</v>
+        <v>5.148824032882333</v>
       </c>
       <c r="D8" t="n">
-        <v>31.56860994269359</v>
+        <v>5.129899115687708</v>
       </c>
       <c r="E8" t="n">
-        <v>12.33220961866323</v>
+        <v>2.003984063032775</v>
       </c>
       <c r="F8" t="n">
-        <v>6.832844328264919</v>
+        <v>1.110337203343049</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>19.88726286450088</v>
+        <v>3.231680215481393</v>
       </c>
       <c r="D9" t="n">
-        <v>20.09602623357594</v>
+        <v>3.265604262956091</v>
       </c>
       <c r="E9" t="n">
-        <v>12.33220961866323</v>
+        <v>2.003984063032775</v>
       </c>
       <c r="F9" t="n">
-        <v>6.832844328264919</v>
+        <v>1.110337203343049</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
